--- a/ontology/ontology-codegen v2/datasource/SkosVocabulary.xlsx
+++ b/ontology/ontology-codegen v2/datasource/SkosVocabulary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F004EE5-C14B-4750-90C6-C9E2F8A45406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1C3FD161-D8D5-4061-9DD1-3DB30ABB8FE0}"/>
+    <workbookView xWindow="30615" yWindow="1920" windowWidth="23040" windowHeight="11250" activeTab="2" xr2:uid="{1C3FD161-D8D5-4061-9DD1-3DB30ABB8FE0}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -28898,12 +28898,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="72ccbf35-dcc7-4590-9537-6d71d0e4df17">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <TaxCatchAll xmlns="b5134ab8-3d65-4fc5-b690-e8cc6b15e593" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -29153,22 +29157,22 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="72ccbf35-dcc7-4590-9537-6d71d0e4df17">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <TaxCatchAll xmlns="b5134ab8-3d65-4fc5-b690-e8cc6b15e593" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767417FB-96C0-404E-BAD3-1F2A089AF595}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1196BE52-4412-4FF2-8EB5-C31823633ED9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="72ccbf35-dcc7-4590-9537-6d71d0e4df17"/>
+    <ds:schemaRef ds:uri="b5134ab8-3d65-4fc5-b690-e8cc6b15e593"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -29194,13 +29198,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1196BE52-4412-4FF2-8EB5-C31823633ED9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{767417FB-96C0-404E-BAD3-1F2A089AF595}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="72ccbf35-dcc7-4590-9537-6d71d0e4df17"/>
-    <ds:schemaRef ds:uri="b5134ab8-3d65-4fc5-b690-e8cc6b15e593"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
